--- a/StructureDefinition-corrected-intraocular-pressure.xlsx
+++ b/StructureDefinition-corrected-intraocular-pressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-corrected-intraocular-pressure.xlsx
+++ b/StructureDefinition-corrected-intraocular-pressure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1905,17 +1905,17 @@
   <dimension ref="A1:AP60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.57421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.25390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.77734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="123.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1924,28 +1924,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.55078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-corrected-intraocular-pressure.xlsx
+++ b/StructureDefinition-corrected-intraocular-pressure.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2338" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2377" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:17:00-03:00</t>
+    <t>2026-10-20T20:13:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -631,6 +631,31 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:exam</t>
+  </si>
+  <si>
+    <t>exam</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -642,18 +667,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -661,7 +674,7 @@
 </t>
   </si>
   <si>
-    <t>Identifies this as a corrected IOP reading</t>
+    <t>Identifies this as a corrected IOP reading. LOINC 96093-0/96092-2 (compensated IOP) exist but may not be equivalent to CCT-based correction; not used</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -671,6 +684,15 @@
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="corrected-intraocular-pressure"/&gt;
+    &lt;display value="Intraocular pressure corrected for central corneal thickness"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>example</t>
@@ -1065,9 +1087,6 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -1077,7 +1096,7 @@
     <t>bodySiteEye</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.3.0}
 </t>
   </si>
   <si>
@@ -1902,7 +1921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP60"/>
+  <dimension ref="A1:AP61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.25390625" customWidth="true" bestFit="true"/>
@@ -3638,7 +3657,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>191</v>
       </c>
@@ -3688,7 +3707,7 @@
         <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>83</v>
@@ -3706,25 +3725,23 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>191</v>
@@ -3751,10 +3768,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3762,14 +3779,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3785,22 +3804,22 @@
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3810,7 +3829,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3825,13 +3844,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3849,13 +3868,13 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -3864,34 +3883,34 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3910,19 +3929,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -3932,7 +3951,7 @@
         <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>83</v>
@@ -3947,13 +3966,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -3971,10 +3990,10 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>94</v>
@@ -3986,30 +4005,30 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>83</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4017,13 +4036,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>83</v>
@@ -4032,18 +4051,20 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4091,13 +4112,13 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>83</v>
@@ -4106,44 +4127,44 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AP18" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
+      <c r="A19" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AO18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>233</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>234</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>83</v>
@@ -4152,20 +4173,18 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4213,13 +4232,13 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
@@ -4228,19 +4247,19 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4248,14 +4267,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4274,19 +4293,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4335,7 +4354,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4350,34 +4369,34 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4387,7 +4406,7 @@
         <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>83</v>
@@ -4396,18 +4415,20 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4455,7 +4476,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4470,30 +4491,30 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AP21" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" hidden="true">
+      <c r="A22" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AN21" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>263</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4504,10 +4525,10 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>83</v>
@@ -4516,18 +4537,18 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4575,13 +4596,13 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
@@ -4590,19 +4611,19 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>268</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -4610,10 +4631,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4621,10 +4642,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>95</v>
@@ -4636,19 +4657,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4697,45 +4716,45 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4743,34 +4762,34 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4795,13 +4814,13 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4819,7 +4838,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4828,7 +4847,7 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
@@ -4837,38 +4856,38 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4883,16 +4902,16 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4917,40 +4936,40 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
@@ -4959,31 +4978,31 @@
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4993,7 +5012,7 @@
         <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>83</v>
@@ -5002,19 +5021,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5039,13 +5058,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5063,7 +5082,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5081,27 +5100,27 @@
         <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5112,7 +5131,7 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>95</v>
@@ -5124,18 +5143,20 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5159,13 +5180,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5183,13 +5204,13 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>83</v>
@@ -5201,27 +5222,27 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5235,7 +5256,7 @@
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>
@@ -5244,15 +5265,17 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>324</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5277,13 +5300,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5301,7 +5324,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5313,44 +5336,44 @@
         <v>83</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5362,17 +5385,15 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5409,73 +5430,71 @@
         <v>83</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AC29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AG29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AF29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>83</v>
@@ -5484,15 +5503,17 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>337</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>338</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5529,19 +5550,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5565,7 +5586,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5574,14 +5595,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="B31" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5593,7 +5616,7 @@
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>83</v>
@@ -5602,13 +5625,13 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5659,19 +5682,19 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
@@ -5683,7 +5706,7 @@
         <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>328</v>
+        <v>83</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5694,10 +5717,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5708,7 +5731,7 @@
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5720,13 +5743,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5765,43 +5788,43 @@
         <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AC32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AD32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE32" t="s" s="2">
+      <c r="AG32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5823,10 +5846,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5838,7 +5861,7 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>348</v>
@@ -5846,16 +5869,14 @@
       <c r="M33" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N33" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -5885,31 +5906,31 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -5921,7 +5942,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -5932,10 +5953,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5958,22 +5979,24 @@
         <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>355</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6015,10 +6038,10 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>94</v>
@@ -6027,7 +6050,7 @@
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6050,10 +6073,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6061,10 +6084,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6073,23 +6096,19 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>364</v>
-      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6137,13 +6156,13 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -6158,10 +6177,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>367</v>
+        <v>137</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6172,10 +6191,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6186,7 +6205,7 @@
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6198,19 +6217,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6259,13 +6278,13 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
@@ -6280,10 +6299,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6294,10 +6313,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6317,22 +6336,22 @@
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>329</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6357,13 +6376,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6381,7 +6400,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6402,10 +6421,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6416,10 +6435,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6442,18 +6461,20 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>386</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6477,13 +6498,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6501,7 +6522,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6519,27 +6540,27 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6562,16 +6583,16 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6621,7 +6642,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6639,27 +6660,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6670,7 +6691,7 @@
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>83</v>
@@ -6682,20 +6703,18 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6743,45 +6762,45 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM40" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6792,7 +6811,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6804,16 +6823,20 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6861,19 +6884,19 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>407</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>83</v>
+        <v>413</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -6882,10 +6905,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>83</v>
+        <v>414</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>328</v>
+        <v>415</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6896,21 +6919,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6922,17 +6945,15 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -6981,19 +7002,19 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -7005,7 +7026,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7016,14 +7037,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7036,26 +7057,24 @@
         <v>83</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7103,7 +7122,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7127,7 +7146,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7138,42 +7157,46 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7221,19 +7244,19 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>423</v>
+        <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7242,10 +7265,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>425</v>
+        <v>137</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7256,10 +7279,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7282,13 +7305,13 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7339,7 +7362,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7348,7 +7371,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7360,7 +7383,7 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>429</v>
@@ -7400,7 +7423,7 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>192</v>
+        <v>424</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>431</v>
@@ -7408,12 +7431,8 @@
       <c r="M46" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>434</v>
-      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7437,13 +7456,13 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>435</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>436</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -7470,7 +7489,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7479,13 +7498,13 @@
         <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>437</v>
+        <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>303</v>
+        <v>433</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7496,10 +7515,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7510,7 +7529,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7525,16 +7544,16 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7559,13 +7578,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7583,13 +7602,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -7601,13 +7620,13 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7618,10 +7637,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7632,7 +7651,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7644,17 +7663,19 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7679,13 +7700,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>448</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>449</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7703,13 +7724,13 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
@@ -7721,13 +7742,13 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>441</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>451</v>
+        <v>308</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7738,10 +7759,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7764,16 +7785,18 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>324</v>
+        <v>451</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7821,7 +7844,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7842,7 +7865,7 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>455</v>
@@ -7870,7 +7893,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7879,20 +7902,18 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7947,7 +7968,7 @@
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
@@ -7962,10 +7983,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>461</v>
+        <v>428</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -7974,12 +7995,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7987,13 +8008,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>83</v>
@@ -8002,16 +8023,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8061,7 +8082,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8082,10 +8103,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8094,12 +8115,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8107,13 +8128,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>83</v>
@@ -8122,20 +8143,18 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>404</v>
+        <v>468</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>473</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8183,7 +8202,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8204,10 +8223,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8218,10 +8237,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8232,7 +8251,7 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8241,19 +8260,23 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>324</v>
+        <v>408</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>325</v>
+        <v>474</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8301,19 +8324,19 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>327</v>
+        <v>473</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>83</v>
@@ -8322,10 +8345,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>83</v>
+        <v>478</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>328</v>
+        <v>479</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8336,21 +8359,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8362,17 +8385,15 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>141</v>
+        <v>330</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8421,19 +8442,19 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -8445,7 +8466,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8456,14 +8477,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>415</v>
+        <v>139</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8476,26 +8497,24 @@
         <v>83</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>417</v>
+        <v>335</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O55" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8543,7 +8562,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>418</v>
+        <v>338</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8567,7 +8586,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>137</v>
+        <v>333</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8578,45 +8597,45 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>481</v>
+        <v>421</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>482</v>
+        <v>143</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8641,13 +8660,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8665,34 +8684,34 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>479</v>
+        <v>422</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>483</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -8700,10 +8719,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8711,7 +8730,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>94</v>
@@ -8726,19 +8745,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>487</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8763,13 +8782,13 @@
         <v>83</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -8787,10 +8806,10 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>94</v>
@@ -8805,27 +8824,27 @@
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8845,22 +8864,22 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>489</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>490</v>
       </c>
       <c r="M58" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="N58" t="s" s="2">
-        <v>492</v>
-      </c>
       <c r="O58" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8885,13 +8904,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -8909,7 +8928,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8918,7 +8937,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -8927,19 +8946,19 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>83</v>
+        <v>492</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -8951,14 +8970,14 @@
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
@@ -8973,16 +8992,16 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>295</v>
+        <v>494</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>296</v>
+        <v>495</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>297</v>
+        <v>496</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9007,13 +9026,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9037,10 +9056,10 @@
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9049,31 +9068,31 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9092,19 +9111,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>495</v>
+        <v>300</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>496</v>
+        <v>301</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>408</v>
+        <v>303</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9129,13 +9148,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9153,7 +9172,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9171,23 +9190,145 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>410</v>
+        <v>307</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AO60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP60" t="s" s="2">
+      <c r="O61" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP60">
+  <autoFilter ref="A1:AP61">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9197,7 +9338,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI59">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
